--- a/automation/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/automation/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Test ID</t>
   </si>
@@ -26,48 +26,6 @@
   </si>
   <si>
     <t>Failure Reason</t>
-  </si>
-  <si>
-    <t>TC_AUTH_010</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Authentication Test Scenario #10 - Validate authentication component behavior 10</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>OTP validation mismatch on invalid input</t>
-  </si>
-  <si>
-    <t>TC_FORM_008</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms Test Scenario #8 - Validate forms component behavior 8</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>Validation message missing on mandatory field submit</t>
-  </si>
-  <si>
-    <t>TC_UPLD_002</t>
-  </si>
-  <si>
-    <t>File Upload</t>
-  </si>
-  <si>
-    <t>File Upload Test Scenario #2 - Validate file upload component behavior 2</t>
-  </si>
-  <si>
-    <t>Application crash on large binary file upload</t>
   </si>
 </sst>
 </file>
@@ -454,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -481,57 +439,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
